--- a/out/Attention-S4_repeat_3_000008.xlsx
+++ b/out/Attention-S4_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.225252353036832</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001142616813916247</v>
+        <v>-0.0001479806622392498</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1312647259402678</v>
+        <v>-0.1700013586069815</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6252523530368315</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.225252353036832</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1314795495775663</v>
+        <v>-0.1702637978301798</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3615976346533492</v>
+        <v>0.4115666615996745</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5924105149078038</v>
+        <v>0.6536602629093812</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02576375554948644</v>
+        <v>0.02932403822811901</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2817599080760481</v>
+        <v>0.300081038684669</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04518084897832406</v>
+        <v>0.05142437173316745</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.346349436262178</v>
+        <v>0.373596141552849</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05488939569274302</v>
+        <v>0.06247453848569182</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4109434471725125</v>
+        <v>0.447116321219736</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01452510936493911</v>
+        <v>0.01653232819520267</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3850338969967116</v>
+        <v>0.4176263816925171</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008068397792159461</v>
+        <v>0.009184057279842683</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6252523530368315</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3866328330489141</v>
+        <v>0.4194469599233337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01695460296271192</v>
+        <v>0.01929832295783005</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4124841723849815</v>
+        <v>0.4488705213361608</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006658327080978363</v>
+        <v>0.007578743035457382</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4088307991634531</v>
+        <v>0.4447131925260534</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004740296556861865</v>
+        <v>0.005395771908227734</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4116502888012202</v>
+        <v>0.4479228334042251</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001862100398412693</v>
+        <v>0.002120099726193355</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4106318586680901</v>
+        <v>0.4467644164324326</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001055492258902515</v>
+        <v>0.001201926509768414</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4108782961310181</v>
+        <v>0.4470455727310849</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003989830153545123</v>
+        <v>0.0004541783691965532</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4106199221246433</v>
+        <v>0.4467522132796189</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001843651962675816</v>
+        <v>0.0002107882469095697</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4105893821407305</v>
+        <v>0.4467181095770202</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.44299753144418e-05</v>
+        <v>7.41178788466895e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4105337180447674</v>
+        <v>0.446655376072318</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>1.837230183129111e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4105002426924885</v>
+        <v>0.4466179274150703</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4104952270550057</v>
+        <v>0.4466129095436614</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.418340913531692</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4104910268456833</v>
+        <v>0.4466088187910742</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4104880429665777</v>
+        <v>0.4466062013876554</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4104825992215714</v>
+        <v>0.4466006841456657</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.418340913531692</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.410476606488141</v>
+        <v>0.4465943601516578</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4104712386995626</v>
+        <v>0.4465889923630795</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4104712754480543</v>
+        <v>0.4465890291115712</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4104713856935299</v>
+        <v>0.4465891393570467</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4104714591905135</v>
+        <v>0.4465892128540303</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4104716429329726</v>
+        <v>0.4465893965964895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4104731863696291</v>
+        <v>0.4465909400331459</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.818340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4104746563093022</v>
+        <v>0.446592409972819</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4104759057580242</v>
+        <v>0.4465936594215411</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4104772654522215</v>
+        <v>0.4465950191157383</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4104750605427122</v>
+        <v>0.446592814206229</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4104746563093022</v>
+        <v>0.446592409972819</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4104743623213675</v>
+        <v>0.4465921159848843</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4104740315849411</v>
+        <v>0.4465917852484579</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4104737375970066</v>
+        <v>0.4465914912605234</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4104733701120883</v>
+        <v>0.4465911237756051</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4104732598666127</v>
+        <v>0.4465910135301296</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.410473223118121</v>
+        <v>0.4465909767816379</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4104733701120883</v>
+        <v>0.4465911237756051</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4104728923816947</v>
+        <v>0.4465906460452115</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4104738478424819</v>
+        <v>0.4465916015059987</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4104734803575638</v>
+        <v>0.4465912340210806</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4104739213394658</v>
+        <v>0.4465916750029826</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4104732966151047</v>
+        <v>0.4465910502786215</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4104731128726455</v>
+        <v>0.4465908665361623</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4104727086392355</v>
+        <v>0.4465904623027523</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4104718634239235</v>
+        <v>0.4465896170874403</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4104718266754318</v>
+        <v>0.4465895803389486</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.410471973669399</v>
+        <v>0.4465897273329159</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4104719001724154</v>
+        <v>0.4465896538359322</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.410471973669399</v>
+        <v>0.4465897273329159</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4104720104178909</v>
+        <v>0.4465897640814078</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4104719001724154</v>
+        <v>0.4465896538359322</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4104723411543174</v>
+        <v>0.4465900948178342</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4104722309088418</v>
+        <v>0.4465899845723587</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4104721941603499</v>
+        <v>0.4465899478238667</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4104721206633663</v>
+        <v>0.4465898743268831</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4104720839148746</v>
+        <v>0.4465898375783914</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4104718634239235</v>
+        <v>0.4465896170874403</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4104717899269399</v>
+        <v>0.4465895435904567</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4104717164299563</v>
+        <v>0.4465894700934731</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4104717531784482</v>
+        <v>0.446589506841965</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6252523530368315</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4104716429329726</v>
+        <v>0.4465893965964895</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.225252353036832</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4104717531784482</v>
+        <v>0.446589506841965</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4104720471663826</v>
+        <v>0.4465898008298995</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000008.xlsx
+++ b/out/Attention-S4_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.4490589350268095</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618353</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.225252353036832</v>
+        <v>0.09878029543816469</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917839</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618354</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001142616813916247</v>
+        <v>-0.0001135592026240192</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1312647259402678</v>
+        <v>-0.1304577127597113</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618353</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.1012197045618354</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618354</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.225252353036832</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.225252353036832</v>
+        <v>0.09878029543816469</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1313789876216595</v>
+        <v>-0.1305712719623353</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1314795495775663</v>
+        <v>-0.1306407378510394</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3615976346533492</v>
+        <v>0.2497835155763985</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5924105149078038</v>
+        <v>0.3694058867984232</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02576375554948644</v>
+        <v>0.01779702304129014</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2817599080760481</v>
+        <v>0.1548157371290109</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04518084897832406</v>
+        <v>0.03120991459291778</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.346349436262178</v>
+        <v>0.1994326039937001</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05488939569274302</v>
+        <v>0.03791636036873169</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4109434471725125</v>
+        <v>0.2440524404983174</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01452510936493911</v>
+        <v>0.01003277292104251</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3850338969967116</v>
+        <v>0.226154228221383</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008068397792159461</v>
+        <v>0.005571829948133054</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.09878029543816463</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3866328330489141</v>
+        <v>0.227257184324401</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01695460296271192</v>
+        <v>0.01171128148243897</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4124841723849815</v>
+        <v>0.2451136221064595</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006658327080978363</v>
+        <v>0.004597079772395089</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4088307991634531</v>
+        <v>0.2425885134271379</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004740296556861865</v>
+        <v>0.00327237675682935</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4116502888012202</v>
+        <v>0.2445347841080439</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001862100398412693</v>
+        <v>0.001284996638903315</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4106318586680901</v>
+        <v>0.2438294824298157</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001055492258902515</v>
+        <v>0.0007271712543294979</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4108782961310181</v>
+        <v>0.2439982603508951</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003989830153545123</v>
+        <v>0.0002744998769022498</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.225252353036832</v>
+        <v>0.09878029543816469</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4106199221246433</v>
+        <v>0.2438179608929965</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001843651962675816</v>
+        <v>0.0001260142927665245</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917838</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4105893821407305</v>
+        <v>0.2437952907878473</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.44299753144418e-05</v>
+        <v>4.263219236688449e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4105337180447674</v>
+        <v>0.2437552388736124</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4105002426924885</v>
+        <v>0.243730372348767</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4104952270550057</v>
+        <v>0.2437253611791362</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4104910268456833</v>
+        <v>0.243720906885332</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4104880429665777</v>
+        <v>0.24371737278808</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4104825992215714</v>
+        <v>0.2437120769580759</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.410476606488141</v>
+        <v>0.2437064149610721</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4104712386995626</v>
+        <v>0.243706231218613</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4104712754480543</v>
+        <v>0.2437062679671047</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4104713856935299</v>
+        <v>0.2437063782125802</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4104714591905135</v>
+        <v>0.2437064517095638</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.5968981654917838</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4104716429329726</v>
+        <v>0.243706635452023</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.225252353036832</v>
+        <v>-0.5968981654917838</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4104731863696291</v>
+        <v>0.2437081788886795</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.818340913531692</v>
+        <v>0.09878029543816458</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4104746563093022</v>
+        <v>0.2437096488283526</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.225252353036832</v>
+        <v>0.09878029543816458</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4104759057580242</v>
+        <v>0.2437108982770746</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4104772654522215</v>
+        <v>0.2437122579712719</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4104750605427122</v>
+        <v>0.2437100530617626</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4104746563093022</v>
+        <v>0.2437096488283526</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.2437088036130406</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4104743623213675</v>
+        <v>0.2437093548404179</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4104740315849411</v>
+        <v>0.2437090241039915</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4104737375970066</v>
+        <v>0.243708730116057</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.2437088036130406</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4104733701120883</v>
+        <v>0.2437083626311387</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4104732598666127</v>
+        <v>0.2437082523856631</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.410473223118121</v>
+        <v>0.2437082156371714</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4104733701120883</v>
+        <v>0.2437083626311387</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4104728923816947</v>
+        <v>0.243707884900745</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4104738478424819</v>
+        <v>0.2437088403615323</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4104738110939902</v>
+        <v>0.2437088036130406</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618355</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4104734803575638</v>
+        <v>0.2437084728766142</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.7968981654917839</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4104739213394658</v>
+        <v>0.2437089138585161</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4104732966151047</v>
+        <v>0.243708289134155</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4104731128726455</v>
+        <v>0.2437081053916959</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4104727086392355</v>
+        <v>0.2437077011582858</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4104718634239235</v>
+        <v>0.2437068559429739</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4104718266754318</v>
+        <v>0.2437068191944822</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-2.418340913531692</v>
+        <v>-1.492576626421732</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.410471973669399</v>
+        <v>0.2437069661884494</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.796898165491784</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4104719001724154</v>
+        <v>0.2437068926914658</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.225252353036832</v>
+        <v>0.09878029543816449</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.410471973669399</v>
+        <v>0.2437069661884494</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4104720104178909</v>
+        <v>0.2437070029369413</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4104719001724154</v>
+        <v>0.2437068926914658</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4104723411543174</v>
+        <v>0.2437073336733677</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4104722309088418</v>
+        <v>0.2437072234278922</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4104721941603499</v>
+        <v>0.2437071866794003</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4104721206633663</v>
+        <v>0.2437071131824166</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4104720839148746</v>
+        <v>0.2437070764339249</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.225252353036832</v>
+        <v>0.794458756368113</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4104718634239235</v>
+        <v>0.2437068559429739</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618355</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4104717899269399</v>
+        <v>0.2437067824459903</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.1012197045618355</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4104717164299563</v>
+        <v>0.2437067089490066</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6252523530368315</v>
+        <v>-0.1012197045618355</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4104717531784482</v>
+        <v>0.2437067456974986</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6252523530368315</v>
+        <v>0.594458756368113</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4104716429329726</v>
+        <v>0.243706635452023</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.225252353036832</v>
+        <v>-0.1012197045618355</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4104717531784482</v>
+        <v>0.2437067456974986</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-2.418340913531692</v>
+        <v>-0.4490589350268098</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4104720471663826</v>
+        <v>0.243707039685433</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_3_000008.xlsx
+++ b/out/Attention-S4_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00253383070230484</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.4490589350268095</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.0005325525999069214</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1012197045618353</v>
+        <v>-0.79</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.003706201910972595</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.003988031297922134</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.09878029543816469</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.003349427133798599</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001243487000465393</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001250322908163071</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.00203598290681839</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001092500984668732</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001071009784936905</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7968981654917839</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001311071217060089</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1012197045618354</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002237312495708466</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.794458756368113</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.004153478890657425</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.794458756368113</v>
+        <v>0.3</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.004463307559490204</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.794458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.003851395100355148</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.794458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001566153019666672</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.003268685191869736</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.004633050411939621</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.004593227058649063</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.004103139042854309</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.005074061453342438</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.007309280335903168</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.009274788200855255</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.008322525769472122</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.006928395479917526</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.594458756368113</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.007708277553319931</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.594458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.007874999195337296</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.007336992770433426</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.007994912564754486</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.009939763695001602</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01157734915614128</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.005698967725038528</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.594458756368113</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.008161481469869614</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.00835716724395752</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00717506930232048</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.007860179990530014</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.007462214678525925</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.007657986134290695</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.594458756368113</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.009345613420009613</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.594458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01035670191049576</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.594458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.009837094694375992</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01190467551350594</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.594458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01760143414139748</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.594458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01708199456334114</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001135592026240192</v>
+        <v>-9.635026616114191e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1304577127597113</v>
+        <v>-0.1106879500447793</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004988163709640503</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.006241276860237122</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.0003027655184268951</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.002036422491073608</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0009514540433883667</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1012197045618353</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-8.960068225860596e-05</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1012197045618354</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0003047846257686615</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1012197045618354</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.002017293125391006</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.001902233809232712</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.002436205744743347</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.000586874783039093</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.09878029543816469</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0008131563663482666</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001281976699829102</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1305712719623353</v>
+        <v>-0.1107843003109405</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.001883834600448608</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1306407378510394</v>
+        <v>-0.1108507915076072</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2497835155763985</v>
+        <v>0.2390869437217567</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002171631902456284</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3694058867984232</v>
+        <v>0.3677826661018014</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01779702304129014</v>
+        <v>0.01703493112872112</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.002970132976770401</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1548157371290109</v>
+        <v>0.16238154862056</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03120991459291778</v>
+        <v>0.02987333671938833</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.0003432892262935638</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1994326039937001</v>
+        <v>0.2050878629179367</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03791636036873169</v>
+        <v>0.03629257610098763</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001778114587068558</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2440524404983174</v>
+        <v>0.2477972034216072</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01003277292104251</v>
+        <v>0.009603224122599112</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002761948853731155</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7968981654917838</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.226154228221383</v>
+        <v>0.2306649810307056</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005571829948133054</v>
+        <v>0.005332995904567852</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0056438148021698</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.09878029543816463</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.227257184324401</v>
+        <v>0.2317204892355725</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01171128148243897</v>
+        <v>0.01120878078999389</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01077502593398094</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.794458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2451136221064595</v>
+        <v>0.2488120420935699</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004597079772395089</v>
+        <v>0.004400885845256141</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.008341602981090546</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2425885134271379</v>
+        <v>0.2463946862629773</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00327237675682935</v>
+        <v>0.003132657010880309</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.005600340664386749</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.794458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2445347841080439</v>
+        <v>0.2482572786479641</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001284996638903315</v>
+        <v>0.001229323099750646</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.005082651972770691</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.794458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2438294824298157</v>
+        <v>0.2475821846559735</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007271712543294979</v>
+        <v>0.0006963429909893085</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.002000946551561356</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.794458756368113</v>
+        <v>0.16</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2439982603508951</v>
+        <v>0.2477434696060205</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002744998769022498</v>
+        <v>0.0002615818153647509</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.00240914523601532</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.09878029543816469</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2438179608929965</v>
+        <v>0.2475709047389887</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001260142927665245</v>
+        <v>0.0001205094905494436</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002628330141305923</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7968981654917838</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2437952907878473</v>
+        <v>0.2475489770752324</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.263219236688449e-05</v>
+        <v>4.101754177817654e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003006022423505783</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2437552388736124</v>
+        <v>0.247510397383722</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00369684025645256</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.243730372348767</v>
+        <v>0.2474865245574396</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.154786274885033e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.005377683788537979</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2437253611791362</v>
+        <v>0.247481514132451</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004660326987504959</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.243720906885332</v>
+        <v>0.2474770598386468</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004972491413354874</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.24371737278808</v>
+        <v>0.2474735257413948</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003594424575567245</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2437120769580759</v>
+        <v>0.2474682299113907</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.00534990057349205</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2437064149610721</v>
+        <v>0.247462567914387</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.004374496638774872</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.243706231218613</v>
+        <v>0.2474623841719278</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003695711493492126</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2437062679671047</v>
+        <v>0.2474624209204195</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.006028857082128525</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2437063782125802</v>
+        <v>0.2474625311658951</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0064501091837883</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2437064517095638</v>
+        <v>0.2474626046628787</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.004153843969106674</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5968981654917838</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.243706635452023</v>
+        <v>0.2474627884053378</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>5.976110696792603e-05</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5968981654917838</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2437081788886795</v>
+        <v>0.2474643318419943</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.004135355353355408</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.09878029543816458</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2437096488283526</v>
+        <v>0.2474658017816674</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01705572381615639</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.09878029543816458</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2437108982770746</v>
+        <v>0.2474670512303894</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.03996090218424797</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.794458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2437122579712719</v>
+        <v>0.2474684109245867</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02393318526446819</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.794458756368113</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2437100530617626</v>
+        <v>0.2474662060150774</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01626944169402122</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.794458756368113</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2437096488283526</v>
+        <v>0.2474658017816674</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01594160869717598</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.794458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2437088036130406</v>
+        <v>0.2474649565663554</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01603342220187187</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.794458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2437093548404179</v>
+        <v>0.2474655077937327</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01521322131156921</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.794458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2437090241039915</v>
+        <v>0.2474651770573063</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01536842808127403</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.243708730116057</v>
+        <v>0.2474648830693718</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.01210235059261322</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2437088036130406</v>
+        <v>0.2474649565663554</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.008092310279607773</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2437083626311387</v>
+        <v>0.2474645155844535</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.008501026779413223</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.16</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2437082523856631</v>
+        <v>0.2474644053389779</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01103974506258965</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2437082156371714</v>
+        <v>0.2474643685904862</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01682348176836967</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.594458756368113</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2437083626311387</v>
+        <v>0.2474645155844535</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02153516560792923</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.594458756368113</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.243707884900745</v>
+        <v>0.2474640378540598</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02051825821399689</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.594458756368113</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2437088403615323</v>
+        <v>0.2474649933148471</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.003928586840629578</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2437088036130406</v>
+        <v>0.2474649565663554</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.000247512012720108</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1012197045618355</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2437084728766142</v>
+        <v>0.247464625829929</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.005196254700422287</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7968981654917839</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2437089138585161</v>
+        <v>0.247465066811831</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.007579270750284195</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.243708289134155</v>
+        <v>0.2474644420874698</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.002290878444910049</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2437081053916959</v>
+        <v>0.2474642583450107</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006254542618989944</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2437077011582858</v>
+        <v>0.2474638541116007</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006847281008958817</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2437068559429739</v>
+        <v>0.2474630088962887</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.003031101077795029</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2437068191944822</v>
+        <v>0.247462972147797</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.003542065620422363</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.492576626421732</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2437069661884494</v>
+        <v>0.2474631191417642</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002731554210186005</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.796898165491784</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2437068926914658</v>
+        <v>0.2474630456447806</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.004737775772809982</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.09878029543816449</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2437069661884494</v>
+        <v>0.2474631191417642</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.002174858003854752</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2437070029369413</v>
+        <v>0.2474631558902562</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.004152845591306686</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2437068926914658</v>
+        <v>0.2474630456447806</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.002228144556283951</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2437073336733677</v>
+        <v>0.2474634866266826</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.006005313247442245</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2437072234278922</v>
+        <v>0.247463376381207</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.005843359977006912</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2437071866794003</v>
+        <v>0.2474633396327151</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.002824444323778152</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2437071131824166</v>
+        <v>0.2474632661357315</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.001999173313379288</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2437070764339249</v>
+        <v>0.2474632293872398</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.003798659890890121</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.794458756368113</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2437068559429739</v>
+        <v>0.2474630088962887</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.004138130694627762</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1012197045618355</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2437067824459903</v>
+        <v>0.2474629353993051</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.001121319830417633</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1012197045618355</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2437067089490066</v>
+        <v>0.2474628619023214</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.001979958266019821</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1012197045618355</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2437067456974986</v>
+        <v>0.2474628986508134</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.005019348114728928</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.594458756368113</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.243706635452023</v>
+        <v>0.2474627884053378</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001585096120834351</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1012197045618355</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2437067456974986</v>
+        <v>0.2474628986508134</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.004260767251253128</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4490589350268098</v>
+        <v>-0.1199999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.243707039685433</v>
+        <v>0.2474631926387479</v>
       </c>
     </row>
   </sheetData>
